--- a/outputs/Cross_mechanism_gap_matrix.xlsx
+++ b/outputs/Cross_mechanism_gap_matrix.xlsx
@@ -546,7 +546,7 @@
         <v>13</v>
       </c>
       <c r="H4" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -555,7 +555,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
@@ -620,13 +620,13 @@
         <v>6</v>
       </c>
       <c r="H6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="4" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>23</v>
@@ -642,7 +642,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
@@ -657,7 +657,7 @@
         <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7" s="4" t="n">
         <v>0</v>
@@ -678,8 +678,8 @@
       <c r="B8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>0</v>
+      <c r="C8" t="n">
+        <v>1</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -694,7 +694,7 @@
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" s="4" t="n">
         <v>0</v>
@@ -703,7 +703,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="4" t="n">
         <v>0</v>
@@ -768,16 +768,16 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>6</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -790,22 +790,22 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="G11" s="4" t="n">
-        <v>0</v>
+      <c r="G11" t="n">
+        <v>1</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I11" s="4" t="n">
         <v>0</v>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -828,7 +828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:Q6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -846,6 +846,8 @@
     <col width="16" customWidth="1" min="13" max="13"/>
     <col width="16" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,50 +888,60 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
+          <t>Field - bulb/propeller turbine</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
           <t>Field - hydropower structure (other)</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Field - shaft hydropower</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Field - weir</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Lab - barotrauma chamber</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Lab - blade-strike rig</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Lab - other apparatus</t>
         </is>
       </c>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="M3" s="3" t="inlineStr">
         <is>
           <t>Lab - shear jet/flume</t>
         </is>
       </c>
-      <c r="M3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>Not reported</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr">
         <is>
           <t>Numerical / CFD model</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>Physical model / test rig</t>
         </is>
       </c>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>Review / synthesis</t>
         </is>
@@ -959,28 +971,34 @@
       <c r="G4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="H4" t="n">
-        <v>1</v>
+      <c r="H4" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>2</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>7</v>
       </c>
     </row>
@@ -1003,33 +1021,39 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>4</v>
       </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>3</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>5</v>
       </c>
     </row>
@@ -1060,25 +1084,31 @@
       <c r="H6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>1</v>
+      <c r="I6" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
         <v>3</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>7</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
+        <v>3</v>
+      </c>
+      <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
+      <c r="P6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
     </row>
@@ -1159,10 +1189,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" t="n">
         <v>13</v>
@@ -1174,7 +1204,7 @@
         <v>3</v>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -1184,16 +1214,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
         <v>5</v>
@@ -1221,7 +1251,7 @@
         <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G6" t="n">
         <v>18</v>
